--- a/public/downloads/attendance-tracker.xlsx
+++ b/public/downloads/attendance-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="58">
   <si>
     <t>Attendance and leave tracker</t>
   </si>
@@ -25,7 +25,7 @@
     <t>What this does</t>
   </si>
   <si>
-    <t>Records daily attendance for a team across one month and totals each code automatically.</t>
+    <t>Records daily attendance for a team across one month and totals every code automatically.</t>
   </si>
   <si>
     <t/>
@@ -34,31 +34,31 @@
     <t>Using it</t>
   </si>
   <si>
-    <t>1. Set the month start date in cell C3. Every column heading follows from it.</t>
+    <t>1. Set the month in the cream cell B3 on the Attendance sheet. Every column heading follows from it.</t>
   </si>
   <si>
     <t>2. Replace the names in column B with your team.</t>
   </si>
   <si>
-    <t>3. Each day, enter a code in the grid. Pick from the dropdown so nothing is mistyped.</t>
-  </si>
-  <si>
-    <t>4. The totals on the right count themselves, and the Summary sheet totals the whole team.</t>
+    <t>3. Each day, pick a code from the dropdown. The totals on the right count themselves.</t>
+  </si>
+  <si>
+    <t>4. The Summary sheet totals the whole team.</t>
   </si>
   <si>
     <t>The codes</t>
   </si>
   <si>
-    <t>P present, H holiday, S sick, L late, R remote, U unpaid leave, X public holiday. The Codes sheet lists them and the dropdown enforces them.</t>
+    <t>P present, H holiday, S sick, L late, R remote, U unpaid leave, X public holiday. Each one colours its own cell so a month reads at a glance.</t>
   </si>
   <si>
     <t>Why the dropdown matters</t>
   </si>
   <si>
-    <t>A tracker breaks when someone types "p" one day and "Present" the next, because COUNTIF counts them as different things. The dropdown makes that impossible, which is why every cell in the grid carries one.</t>
-  </si>
-  <si>
-    <t>Cells with a white background are for you to fill in. Shaded cells hold formulas — changing one replaces the calculation with whatever you typed.</t>
+    <t>A tracker breaks the moment someone types "p" one day and "Present" the next, because COUNTIF treats them as different values. The dropdown makes that impossible, which is why the whole grid carries one.</t>
+  </si>
+  <si>
+    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modelling convention.</t>
   </si>
   <si>
     <t>Codes</t>
@@ -139,10 +139,10 @@
     <t>Attendance and leave</t>
   </si>
   <si>
-    <t>Set the month below, then fill the grid from the dropdowns</t>
-  </si>
-  <si>
-    <t>Month starts</t>
+    <t>Set the month, then fill the grid from the dropdowns</t>
+  </si>
+  <si>
+    <t>Month</t>
   </si>
   <si>
     <t>#</t>
@@ -184,7 +184,7 @@
     <t>Days</t>
   </si>
   <si>
-    <t>Total</t>
+    <t>Total entries</t>
   </si>
   <si>
     <t>Every code entered this month</t>
@@ -198,7 +198,7 @@
     <numFmt numFmtId="164" formatCode="mmmm yyyy"/>
     <numFmt numFmtId="165" formatCode="d"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -208,30 +208,30 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF16324F"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
+      <color rgb="FF0A4A3A"/>
+      <sz val="15"/>
+      <name val="Arial"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF5A6B7B"/>
+      <color rgb="FF4A4A48"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF16324F"/>
+      <color rgb="FF0A4A3A"/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF16324F"/>
+      <color rgb="FF141414"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF5A6B7B"/>
+      <color rgb="FF4A4A48"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
@@ -239,23 +239,40 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF4A4A48"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF16324F"/>
-      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF16324F"/>
+      <color rgb="FF141414"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A4A3A"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
@@ -269,52 +286,52 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF16324F"/>
+        <fgColor rgb="FFE1F5EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E7D5B"/>
+        <fgColor rgb="FF0F6E56"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3D7EA6"/>
+        <fgColor rgb="FF2E6E8E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4F7F9"/>
+        <fgColor rgb="FFFAFAF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB4232B"/>
+        <fgColor rgb="FF7A2020"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD08700"/>
+        <fgColor rgb="FF7A5410"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6B5BA6"/>
+        <fgColor rgb="FF0A4A3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5A6B7B"/>
+        <fgColor rgb="FF4A4A48"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8A8F94"/>
+        <fgColor rgb="FF6E6E6C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDF0CE"/>
+        <fgColor rgb="FFFFFDF0"/>
       </patternFill>
     </fill>
   </fills>
@@ -328,16 +345,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FFE4E4E0"/>
       </left>
       <right style="thin">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FFE4E4E0"/>
       </right>
       <top style="thin">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FFE4E4E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FFE4E4E0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -345,64 +362,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -418,13 +409,27 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -440,7 +445,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF2E7D5B"/>
+          <bgColor rgb="FF0F6E56"/>
         </patternFill>
       </fill>
     </dxf>
@@ -451,7 +456,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF3D7EA6"/>
+          <bgColor rgb="FF2E6E8E"/>
         </patternFill>
       </fill>
     </dxf>
@@ -462,7 +467,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB4232B"/>
+          <bgColor rgb="FF7A2020"/>
         </patternFill>
       </fill>
     </dxf>
@@ -473,7 +478,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD08700"/>
+          <bgColor rgb="FF7A5410"/>
         </patternFill>
       </fill>
     </dxf>
@@ -484,7 +489,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF6B5BA6"/>
+          <bgColor rgb="FF0A4A3A"/>
         </patternFill>
       </fill>
     </dxf>
@@ -495,7 +500,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF5A6B7B"/>
+          <bgColor rgb="FF4A4A48"/>
         </patternFill>
       </fill>
     </dxf>
@@ -506,14 +511,14 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF8A8F94"/>
+          <bgColor rgb="FF6E6E6C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEDF1F4"/>
+          <bgColor rgb="FFFAFAF8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -853,17 +858,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF5A6B7B"/>
+    <tabColor rgb="FF4A4A48"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:B20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="96" customWidth="1"/>
+    <col min="2" max="2" width="94" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -873,88 +878,89 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="4"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+    <row r="9" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
+    <row r="15" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
+    <row r="18" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+    <row r="20" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Italic"Explore Excel&amp;R&amp;"Calibri,Italic"Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -962,18 +968,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF5A6B7B"/>
+    <tabColor rgb="FF4A4A48"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -984,102 +990,103 @@
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Italic"Explore Excel&amp;R&amp;"Calibri,Italic"Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1087,19 +1094,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF16324F"/>
+    <tabColor rgb="FF0F6E56"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="33" width="3.4" customWidth="1"/>
-    <col min="34" max="40" width="5.5" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="33" width="3.1" customWidth="1"/>
+    <col min="34" max="40" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>40</v>
       </c>
@@ -1117,628 +1124,628 @@
       <c r="A2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="17" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="18">
+      <c r="B3" s="19">
         <v>46023</v>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+    <row r="6" ht="26" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="20">
-        <f>IF(MONTH($C$3+0)=MONTH($C$3),$C$3+0,"")</f>
-      </c>
-      <c r="D5" s="20">
-        <f>IF(MONTH($C$3+1)=MONTH($C$3),$C$3+1,"")</f>
-      </c>
-      <c r="E5" s="20">
-        <f>IF(MONTH($C$3+2)=MONTH($C$3),$C$3+2,"")</f>
-      </c>
-      <c r="F5" s="20">
-        <f>IF(MONTH($C$3+3)=MONTH($C$3),$C$3+3,"")</f>
-      </c>
-      <c r="G5" s="20">
-        <f>IF(MONTH($C$3+4)=MONTH($C$3),$C$3+4,"")</f>
-      </c>
-      <c r="H5" s="20">
-        <f>IF(MONTH($C$3+5)=MONTH($C$3),$C$3+5,"")</f>
-      </c>
-      <c r="I5" s="20">
-        <f>IF(MONTH($C$3+6)=MONTH($C$3),$C$3+6,"")</f>
-      </c>
-      <c r="J5" s="20">
-        <f>IF(MONTH($C$3+7)=MONTH($C$3),$C$3+7,"")</f>
-      </c>
-      <c r="K5" s="20">
-        <f>IF(MONTH($C$3+8)=MONTH($C$3),$C$3+8,"")</f>
-      </c>
-      <c r="L5" s="20">
-        <f>IF(MONTH($C$3+9)=MONTH($C$3),$C$3+9,"")</f>
-      </c>
-      <c r="M5" s="20">
-        <f>IF(MONTH($C$3+10)=MONTH($C$3),$C$3+10,"")</f>
-      </c>
-      <c r="N5" s="20">
-        <f>IF(MONTH($C$3+11)=MONTH($C$3),$C$3+11,"")</f>
-      </c>
-      <c r="O5" s="20">
-        <f>IF(MONTH($C$3+12)=MONTH($C$3),$C$3+12,"")</f>
-      </c>
-      <c r="P5" s="20">
-        <f>IF(MONTH($C$3+13)=MONTH($C$3),$C$3+13,"")</f>
-      </c>
-      <c r="Q5" s="20">
-        <f>IF(MONTH($C$3+14)=MONTH($C$3),$C$3+14,"")</f>
-      </c>
-      <c r="R5" s="20">
-        <f>IF(MONTH($C$3+15)=MONTH($C$3),$C$3+15,"")</f>
-      </c>
-      <c r="S5" s="20">
-        <f>IF(MONTH($C$3+16)=MONTH($C$3),$C$3+16,"")</f>
-      </c>
-      <c r="T5" s="20">
-        <f>IF(MONTH($C$3+17)=MONTH($C$3),$C$3+17,"")</f>
-      </c>
-      <c r="U5" s="20">
-        <f>IF(MONTH($C$3+18)=MONTH($C$3),$C$3+18,"")</f>
-      </c>
-      <c r="V5" s="20">
-        <f>IF(MONTH($C$3+19)=MONTH($C$3),$C$3+19,"")</f>
-      </c>
-      <c r="W5" s="20">
-        <f>IF(MONTH($C$3+20)=MONTH($C$3),$C$3+20,"")</f>
-      </c>
-      <c r="X5" s="20">
-        <f>IF(MONTH($C$3+21)=MONTH($C$3),$C$3+21,"")</f>
-      </c>
-      <c r="Y5" s="20">
-        <f>IF(MONTH($C$3+22)=MONTH($C$3),$C$3+22,"")</f>
-      </c>
-      <c r="Z5" s="20">
-        <f>IF(MONTH($C$3+23)=MONTH($C$3),$C$3+23,"")</f>
-      </c>
-      <c r="AA5" s="20">
-        <f>IF(MONTH($C$3+24)=MONTH($C$3),$C$3+24,"")</f>
-      </c>
-      <c r="AB5" s="20">
-        <f>IF(MONTH($C$3+25)=MONTH($C$3),$C$3+25,"")</f>
-      </c>
-      <c r="AC5" s="20">
-        <f>IF(MONTH($C$3+26)=MONTH($C$3),$C$3+26,"")</f>
-      </c>
-      <c r="AD5" s="20">
-        <f>IF(MONTH($C$3+27)=MONTH($C$3),$C$3+27,"")</f>
-      </c>
-      <c r="AE5" s="20">
-        <f>IF(MONTH($C$3+28)=MONTH($C$3),$C$3+28,"")</f>
-      </c>
-      <c r="AF5" s="20">
-        <f>IF(MONTH($C$3+29)=MONTH($C$3),$C$3+29,"")</f>
-      </c>
-      <c r="AG5" s="20">
-        <f>IF(MONTH($C$3+30)=MONTH($C$3),$C$3+30,"")</f>
-      </c>
-      <c r="AH5" s="21" t="s">
+      <c r="C6" s="21">
+        <f>IF(MONTH($B$3+0)=MONTH($B$3),$B$3+0,"")</f>
+      </c>
+      <c r="D6" s="21">
+        <f>IF(MONTH($B$3+1)=MONTH($B$3),$B$3+1,"")</f>
+      </c>
+      <c r="E6" s="21">
+        <f>IF(MONTH($B$3+2)=MONTH($B$3),$B$3+2,"")</f>
+      </c>
+      <c r="F6" s="21">
+        <f>IF(MONTH($B$3+3)=MONTH($B$3),$B$3+3,"")</f>
+      </c>
+      <c r="G6" s="21">
+        <f>IF(MONTH($B$3+4)=MONTH($B$3),$B$3+4,"")</f>
+      </c>
+      <c r="H6" s="21">
+        <f>IF(MONTH($B$3+5)=MONTH($B$3),$B$3+5,"")</f>
+      </c>
+      <c r="I6" s="21">
+        <f>IF(MONTH($B$3+6)=MONTH($B$3),$B$3+6,"")</f>
+      </c>
+      <c r="J6" s="21">
+        <f>IF(MONTH($B$3+7)=MONTH($B$3),$B$3+7,"")</f>
+      </c>
+      <c r="K6" s="21">
+        <f>IF(MONTH($B$3+8)=MONTH($B$3),$B$3+8,"")</f>
+      </c>
+      <c r="L6" s="21">
+        <f>IF(MONTH($B$3+9)=MONTH($B$3),$B$3+9,"")</f>
+      </c>
+      <c r="M6" s="21">
+        <f>IF(MONTH($B$3+10)=MONTH($B$3),$B$3+10,"")</f>
+      </c>
+      <c r="N6" s="21">
+        <f>IF(MONTH($B$3+11)=MONTH($B$3),$B$3+11,"")</f>
+      </c>
+      <c r="O6" s="21">
+        <f>IF(MONTH($B$3+12)=MONTH($B$3),$B$3+12,"")</f>
+      </c>
+      <c r="P6" s="21">
+        <f>IF(MONTH($B$3+13)=MONTH($B$3),$B$3+13,"")</f>
+      </c>
+      <c r="Q6" s="21">
+        <f>IF(MONTH($B$3+14)=MONTH($B$3),$B$3+14,"")</f>
+      </c>
+      <c r="R6" s="21">
+        <f>IF(MONTH($B$3+15)=MONTH($B$3),$B$3+15,"")</f>
+      </c>
+      <c r="S6" s="21">
+        <f>IF(MONTH($B$3+16)=MONTH($B$3),$B$3+16,"")</f>
+      </c>
+      <c r="T6" s="21">
+        <f>IF(MONTH($B$3+17)=MONTH($B$3),$B$3+17,"")</f>
+      </c>
+      <c r="U6" s="21">
+        <f>IF(MONTH($B$3+18)=MONTH($B$3),$B$3+18,"")</f>
+      </c>
+      <c r="V6" s="21">
+        <f>IF(MONTH($B$3+19)=MONTH($B$3),$B$3+19,"")</f>
+      </c>
+      <c r="W6" s="21">
+        <f>IF(MONTH($B$3+20)=MONTH($B$3),$B$3+20,"")</f>
+      </c>
+      <c r="X6" s="21">
+        <f>IF(MONTH($B$3+21)=MONTH($B$3),$B$3+21,"")</f>
+      </c>
+      <c r="Y6" s="21">
+        <f>IF(MONTH($B$3+22)=MONTH($B$3),$B$3+22,"")</f>
+      </c>
+      <c r="Z6" s="21">
+        <f>IF(MONTH($B$3+23)=MONTH($B$3),$B$3+23,"")</f>
+      </c>
+      <c r="AA6" s="21">
+        <f>IF(MONTH($B$3+24)=MONTH($B$3),$B$3+24,"")</f>
+      </c>
+      <c r="AB6" s="21">
+        <f>IF(MONTH($B$3+25)=MONTH($B$3),$B$3+25,"")</f>
+      </c>
+      <c r="AC6" s="21">
+        <f>IF(MONTH($B$3+26)=MONTH($B$3),$B$3+26,"")</f>
+      </c>
+      <c r="AD6" s="21">
+        <f>IF(MONTH($B$3+27)=MONTH($B$3),$B$3+27,"")</f>
+      </c>
+      <c r="AE6" s="21">
+        <f>IF(MONTH($B$3+28)=MONTH($B$3),$B$3+28,"")</f>
+      </c>
+      <c r="AF6" s="21">
+        <f>IF(MONTH($B$3+29)=MONTH($B$3),$B$3+29,"")</f>
+      </c>
+      <c r="AG6" s="21">
+        <f>IF(MONTH($B$3+30)=MONTH($B$3),$B$3+30,"")</f>
+      </c>
+      <c r="AH6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AI5" s="22" t="s">
+      <c r="AI6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="AJ5" s="23" t="s">
+      <c r="AJ6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="AK5" s="24" t="s">
+      <c r="AK6" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="AL5" s="25" t="s">
+      <c r="AL6" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="AM5" s="26" t="s">
+      <c r="AM6" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="AN5" s="27" t="s">
+      <c r="AN6" s="17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A7" s="22">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-      <c r="W6" s="29"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="29"/>
-      <c r="AC6" s="29"/>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="30">
-        <f>COUNTIF($C6:$AG6,"P")</f>
-      </c>
-      <c r="AI6" s="30">
-        <f>COUNTIF($C6:$AG6,"H")</f>
-      </c>
-      <c r="AJ6" s="30">
-        <f>COUNTIF($C6:$AG6,"S")</f>
-      </c>
-      <c r="AK6" s="30">
-        <f>COUNTIF($C6:$AG6,"L")</f>
-      </c>
-      <c r="AL6" s="30">
-        <f>COUNTIF($C6:$AG6,"R")</f>
-      </c>
-      <c r="AM6" s="30">
-        <f>COUNTIF($C6:$AG6,"U")</f>
-      </c>
-      <c r="AN6" s="30">
-        <f>COUNTIF($C6:$AG6,"X")</f>
-      </c>
-    </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="24"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="24"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="24"/>
+      <c r="AH7" s="25">
+        <f>COUNTIF($C7:$AG7,"P")</f>
+      </c>
+      <c r="AI7" s="25">
+        <f>COUNTIF($C7:$AG7,"H")</f>
+      </c>
+      <c r="AJ7" s="25">
+        <f>COUNTIF($C7:$AG7,"S")</f>
+      </c>
+      <c r="AK7" s="25">
+        <f>COUNTIF($C7:$AG7,"L")</f>
+      </c>
+      <c r="AL7" s="25">
+        <f>COUNTIF($C7:$AG7,"R")</f>
+      </c>
+      <c r="AM7" s="25">
+        <f>COUNTIF($C7:$AG7,"U")</f>
+      </c>
+      <c r="AN7" s="25">
+        <f>COUNTIF($C7:$AG7,"X")</f>
+      </c>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A8" s="22">
         <v>2</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="29"/>
-      <c r="W7" s="29"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="29"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="30">
-        <f>COUNTIF($C7:$AG7,"P")</f>
-      </c>
-      <c r="AI7" s="30">
-        <f>COUNTIF($C7:$AG7,"H")</f>
-      </c>
-      <c r="AJ7" s="30">
-        <f>COUNTIF($C7:$AG7,"S")</f>
-      </c>
-      <c r="AK7" s="30">
-        <f>COUNTIF($C7:$AG7,"L")</f>
-      </c>
-      <c r="AL7" s="30">
-        <f>COUNTIF($C7:$AG7,"R")</f>
-      </c>
-      <c r="AM7" s="30">
-        <f>COUNTIF($C7:$AG7,"U")</f>
-      </c>
-      <c r="AN7" s="30">
-        <f>COUNTIF($C7:$AG7,"X")</f>
-      </c>
-    </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="24"/>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
+      <c r="AF8" s="24"/>
+      <c r="AG8" s="24"/>
+      <c r="AH8" s="25">
+        <f>COUNTIF($C8:$AG8,"P")</f>
+      </c>
+      <c r="AI8" s="25">
+        <f>COUNTIF($C8:$AG8,"H")</f>
+      </c>
+      <c r="AJ8" s="25">
+        <f>COUNTIF($C8:$AG8,"S")</f>
+      </c>
+      <c r="AK8" s="25">
+        <f>COUNTIF($C8:$AG8,"L")</f>
+      </c>
+      <c r="AL8" s="25">
+        <f>COUNTIF($C8:$AG8,"R")</f>
+      </c>
+      <c r="AM8" s="25">
+        <f>COUNTIF($C8:$AG8,"U")</f>
+      </c>
+      <c r="AN8" s="25">
+        <f>COUNTIF($C8:$AG8,"X")</f>
+      </c>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A9" s="22">
         <v>3</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
-      <c r="W8" s="29"/>
-      <c r="X8" s="29"/>
-      <c r="Y8" s="29"/>
-      <c r="Z8" s="29"/>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="29"/>
-      <c r="AC8" s="29"/>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="29"/>
-      <c r="AF8" s="29"/>
-      <c r="AG8" s="29"/>
-      <c r="AH8" s="30">
-        <f>COUNTIF($C8:$AG8,"P")</f>
-      </c>
-      <c r="AI8" s="30">
-        <f>COUNTIF($C8:$AG8,"H")</f>
-      </c>
-      <c r="AJ8" s="30">
-        <f>COUNTIF($C8:$AG8,"S")</f>
-      </c>
-      <c r="AK8" s="30">
-        <f>COUNTIF($C8:$AG8,"L")</f>
-      </c>
-      <c r="AL8" s="30">
-        <f>COUNTIF($C8:$AG8,"R")</f>
-      </c>
-      <c r="AM8" s="30">
-        <f>COUNTIF($C8:$AG8,"U")</f>
-      </c>
-      <c r="AN8" s="30">
-        <f>COUNTIF($C8:$AG8,"X")</f>
-      </c>
-    </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="24"/>
+      <c r="AH9" s="25">
+        <f>COUNTIF($C9:$AG9,"P")</f>
+      </c>
+      <c r="AI9" s="25">
+        <f>COUNTIF($C9:$AG9,"H")</f>
+      </c>
+      <c r="AJ9" s="25">
+        <f>COUNTIF($C9:$AG9,"S")</f>
+      </c>
+      <c r="AK9" s="25">
+        <f>COUNTIF($C9:$AG9,"L")</f>
+      </c>
+      <c r="AL9" s="25">
+        <f>COUNTIF($C9:$AG9,"R")</f>
+      </c>
+      <c r="AM9" s="25">
+        <f>COUNTIF($C9:$AG9,"U")</f>
+      </c>
+      <c r="AN9" s="25">
+        <f>COUNTIF($C9:$AG9,"X")</f>
+      </c>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A10" s="22">
         <v>4</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="29"/>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="29"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="30">
-        <f>COUNTIF($C9:$AG9,"P")</f>
-      </c>
-      <c r="AI9" s="30">
-        <f>COUNTIF($C9:$AG9,"H")</f>
-      </c>
-      <c r="AJ9" s="30">
-        <f>COUNTIF($C9:$AG9,"S")</f>
-      </c>
-      <c r="AK9" s="30">
-        <f>COUNTIF($C9:$AG9,"L")</f>
-      </c>
-      <c r="AL9" s="30">
-        <f>COUNTIF($C9:$AG9,"R")</f>
-      </c>
-      <c r="AM9" s="30">
-        <f>COUNTIF($C9:$AG9,"U")</f>
-      </c>
-      <c r="AN9" s="30">
-        <f>COUNTIF($C9:$AG9,"X")</f>
-      </c>
-    </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
+      <c r="AF10" s="24"/>
+      <c r="AG10" s="24"/>
+      <c r="AH10" s="25">
+        <f>COUNTIF($C10:$AG10,"P")</f>
+      </c>
+      <c r="AI10" s="25">
+        <f>COUNTIF($C10:$AG10,"H")</f>
+      </c>
+      <c r="AJ10" s="25">
+        <f>COUNTIF($C10:$AG10,"S")</f>
+      </c>
+      <c r="AK10" s="25">
+        <f>COUNTIF($C10:$AG10,"L")</f>
+      </c>
+      <c r="AL10" s="25">
+        <f>COUNTIF($C10:$AG10,"R")</f>
+      </c>
+      <c r="AM10" s="25">
+        <f>COUNTIF($C10:$AG10,"U")</f>
+      </c>
+      <c r="AN10" s="25">
+        <f>COUNTIF($C10:$AG10,"X")</f>
+      </c>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A11" s="22">
         <v>5</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="29"/>
-      <c r="Y10" s="29"/>
-      <c r="Z10" s="29"/>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="29"/>
-      <c r="AC10" s="29"/>
-      <c r="AD10" s="29"/>
-      <c r="AE10" s="29"/>
-      <c r="AF10" s="29"/>
-      <c r="AG10" s="29"/>
-      <c r="AH10" s="30">
-        <f>COUNTIF($C10:$AG10,"P")</f>
-      </c>
-      <c r="AI10" s="30">
-        <f>COUNTIF($C10:$AG10,"H")</f>
-      </c>
-      <c r="AJ10" s="30">
-        <f>COUNTIF($C10:$AG10,"S")</f>
-      </c>
-      <c r="AK10" s="30">
-        <f>COUNTIF($C10:$AG10,"L")</f>
-      </c>
-      <c r="AL10" s="30">
-        <f>COUNTIF($C10:$AG10,"R")</f>
-      </c>
-      <c r="AM10" s="30">
-        <f>COUNTIF($C10:$AG10,"U")</f>
-      </c>
-      <c r="AN10" s="30">
-        <f>COUNTIF($C10:$AG10,"X")</f>
-      </c>
-    </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A11" s="28">
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="24"/>
+      <c r="V11" s="24"/>
+      <c r="W11" s="24"/>
+      <c r="X11" s="24"/>
+      <c r="Y11" s="24"/>
+      <c r="Z11" s="24"/>
+      <c r="AA11" s="24"/>
+      <c r="AB11" s="24"/>
+      <c r="AC11" s="24"/>
+      <c r="AD11" s="24"/>
+      <c r="AE11" s="24"/>
+      <c r="AF11" s="24"/>
+      <c r="AG11" s="24"/>
+      <c r="AH11" s="25">
+        <f>COUNTIF($C11:$AG11,"P")</f>
+      </c>
+      <c r="AI11" s="25">
+        <f>COUNTIF($C11:$AG11,"H")</f>
+      </c>
+      <c r="AJ11" s="25">
+        <f>COUNTIF($C11:$AG11,"S")</f>
+      </c>
+      <c r="AK11" s="25">
+        <f>COUNTIF($C11:$AG11,"L")</f>
+      </c>
+      <c r="AL11" s="25">
+        <f>COUNTIF($C11:$AG11,"R")</f>
+      </c>
+      <c r="AM11" s="25">
+        <f>COUNTIF($C11:$AG11,"U")</f>
+      </c>
+      <c r="AN11" s="25">
+        <f>COUNTIF($C11:$AG11,"X")</f>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A12" s="22">
         <v>6</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="29"/>
-      <c r="Z11" s="29"/>
-      <c r="AA11" s="29"/>
-      <c r="AB11" s="29"/>
-      <c r="AC11" s="29"/>
-      <c r="AD11" s="29"/>
-      <c r="AE11" s="29"/>
-      <c r="AF11" s="29"/>
-      <c r="AG11" s="29"/>
-      <c r="AH11" s="30">
-        <f>COUNTIF($C11:$AG11,"P")</f>
-      </c>
-      <c r="AI11" s="30">
-        <f>COUNTIF($C11:$AG11,"H")</f>
-      </c>
-      <c r="AJ11" s="30">
-        <f>COUNTIF($C11:$AG11,"S")</f>
-      </c>
-      <c r="AK11" s="30">
-        <f>COUNTIF($C11:$AG11,"L")</f>
-      </c>
-      <c r="AL11" s="30">
-        <f>COUNTIF($C11:$AG11,"R")</f>
-      </c>
-      <c r="AM11" s="30">
-        <f>COUNTIF($C11:$AG11,"U")</f>
-      </c>
-      <c r="AN11" s="30">
-        <f>COUNTIF($C11:$AG11,"X")</f>
-      </c>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="24"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="24"/>
+      <c r="X12" s="24"/>
+      <c r="Y12" s="24"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="24"/>
+      <c r="AD12" s="24"/>
+      <c r="AE12" s="24"/>
+      <c r="AF12" s="24"/>
+      <c r="AG12" s="24"/>
+      <c r="AH12" s="25">
+        <f>COUNTIF($C12:$AG12,"P")</f>
+      </c>
+      <c r="AI12" s="25">
+        <f>COUNTIF($C12:$AG12,"H")</f>
+      </c>
+      <c r="AJ12" s="25">
+        <f>COUNTIF($C12:$AG12,"S")</f>
+      </c>
+      <c r="AK12" s="25">
+        <f>COUNTIF($C12:$AG12,"L")</f>
+      </c>
+      <c r="AL12" s="25">
+        <f>COUNTIF($C12:$AG12,"R")</f>
+      </c>
+      <c r="AM12" s="25">
+        <f>COUNTIF($C12:$AG12,"U")</f>
+      </c>
+      <c r="AN12" s="25">
+        <f>COUNTIF($C12:$AG12,"X")</f>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A13" s="22">
         <v>7</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="29"/>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="29"/>
-      <c r="AB12" s="29"/>
-      <c r="AC12" s="29"/>
-      <c r="AD12" s="29"/>
-      <c r="AE12" s="29"/>
-      <c r="AF12" s="29"/>
-      <c r="AG12" s="29"/>
-      <c r="AH12" s="30">
-        <f>COUNTIF($C12:$AG12,"P")</f>
-      </c>
-      <c r="AI12" s="30">
-        <f>COUNTIF($C12:$AG12,"H")</f>
-      </c>
-      <c r="AJ12" s="30">
-        <f>COUNTIF($C12:$AG12,"S")</f>
-      </c>
-      <c r="AK12" s="30">
-        <f>COUNTIF($C12:$AG12,"L")</f>
-      </c>
-      <c r="AL12" s="30">
-        <f>COUNTIF($C12:$AG12,"R")</f>
-      </c>
-      <c r="AM12" s="30">
-        <f>COUNTIF($C12:$AG12,"U")</f>
-      </c>
-      <c r="AN12" s="30">
-        <f>COUNTIF($C12:$AG12,"X")</f>
-      </c>
-    </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A13" s="28">
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="24"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="24"/>
+      <c r="X13" s="24"/>
+      <c r="Y13" s="24"/>
+      <c r="Z13" s="24"/>
+      <c r="AA13" s="24"/>
+      <c r="AB13" s="24"/>
+      <c r="AC13" s="24"/>
+      <c r="AD13" s="24"/>
+      <c r="AE13" s="24"/>
+      <c r="AF13" s="24"/>
+      <c r="AG13" s="24"/>
+      <c r="AH13" s="25">
+        <f>COUNTIF($C13:$AG13,"P")</f>
+      </c>
+      <c r="AI13" s="25">
+        <f>COUNTIF($C13:$AG13,"H")</f>
+      </c>
+      <c r="AJ13" s="25">
+        <f>COUNTIF($C13:$AG13,"S")</f>
+      </c>
+      <c r="AK13" s="25">
+        <f>COUNTIF($C13:$AG13,"L")</f>
+      </c>
+      <c r="AL13" s="25">
+        <f>COUNTIF($C13:$AG13,"R")</f>
+      </c>
+      <c r="AM13" s="25">
+        <f>COUNTIF($C13:$AG13,"U")</f>
+      </c>
+      <c r="AN13" s="25">
+        <f>COUNTIF($C13:$AG13,"X")</f>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A14" s="22">
         <v>8</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="29"/>
-      <c r="X13" s="29"/>
-      <c r="Y13" s="29"/>
-      <c r="Z13" s="29"/>
-      <c r="AA13" s="29"/>
-      <c r="AB13" s="29"/>
-      <c r="AC13" s="29"/>
-      <c r="AD13" s="29"/>
-      <c r="AE13" s="29"/>
-      <c r="AF13" s="29"/>
-      <c r="AG13" s="29"/>
-      <c r="AH13" s="30">
-        <f>COUNTIF($C13:$AG13,"P")</f>
-      </c>
-      <c r="AI13" s="30">
-        <f>COUNTIF($C13:$AG13,"H")</f>
-      </c>
-      <c r="AJ13" s="30">
-        <f>COUNTIF($C13:$AG13,"S")</f>
-      </c>
-      <c r="AK13" s="30">
-        <f>COUNTIF($C13:$AG13,"L")</f>
-      </c>
-      <c r="AL13" s="30">
-        <f>COUNTIF($C13:$AG13,"R")</f>
-      </c>
-      <c r="AM13" s="30">
-        <f>COUNTIF($C13:$AG13,"U")</f>
-      </c>
-      <c r="AN13" s="30">
-        <f>COUNTIF($C13:$AG13,"X")</f>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="24"/>
+      <c r="AH14" s="25">
+        <f>COUNTIF($C14:$AG14,"P")</f>
+      </c>
+      <c r="AI14" s="25">
+        <f>COUNTIF($C14:$AG14,"H")</f>
+      </c>
+      <c r="AJ14" s="25">
+        <f>COUNTIF($C14:$AG14,"S")</f>
+      </c>
+      <c r="AK14" s="25">
+        <f>COUNTIF($C14:$AG14,"L")</f>
+      </c>
+      <c r="AL14" s="25">
+        <f>COUNTIF($C14:$AG14,"R")</f>
+      </c>
+      <c r="AM14" s="25">
+        <f>COUNTIF($C14:$AG14,"U")</f>
+      </c>
+      <c r="AN14" s="25">
+        <f>COUNTIF($C14:$AG14,"X")</f>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C6:AG13">
+  <conditionalFormatting sqref="C7:AG14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"P"</formula>
     </cfRule>
@@ -1761,27 +1768,19 @@
       <formula>"X"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="8">
-      <formula>AND(C$5&lt;&gt;"",WEEKDAY(C$5,2)&gt;5)</formula>
+      <formula>AND(C$6&lt;&gt;"",WEEKDAY(C$6,2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unknown code" error="Use one of the codes listed on the Codes sheet." sqref="AA10:AG13">
-      <formula1>"P,H,S,L,R,U,X"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unknown code" error="Use one of the codes listed on the Codes sheet." sqref="AA6:AG13">
-      <formula1>"P,H,S,L,R,U,X"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unknown code" error="Use one of the codes listed on the Codes sheet." sqref="C10:AG13">
-      <formula1>"P,H,S,L,R,U,X"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unknown code" error="Use one of the codes listed on the Codes sheet." sqref="C6:AG13">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Unknown code" error="Use one of the codes listed on the Codes sheet." sqref="C7:AG14">
       <formula1>"P,H,S,L,R,U,X"</formula1>
     </dataValidation>
   </dataValidations>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Italic"Explore Excel&amp;R&amp;"Calibri,Italic"Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1789,135 +1788,166 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF2E7D5B"/>
+    <tabColor rgb="FF0A4A3A"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="D4" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="9">
-        <f>SUM(Attendance!AH6:AH13)</f>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="C5" s="22">
+        <f>SUM(Attendance!AH7:AH14)</f>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="11">
-        <f>SUM(Attendance!AI6:AI13)</f>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="C6" s="26">
+        <f>SUM(Attendance!AI7:AI14)</f>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="9">
-        <f>SUM(Attendance!AJ6:AJ13)</f>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="C7" s="22">
+        <f>SUM(Attendance!AJ7:AJ14)</f>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="11">
-        <f>SUM(Attendance!AK6:AK13)</f>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="C8" s="26">
+        <f>SUM(Attendance!AK7:AK14)</f>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="9">
-        <f>SUM(Attendance!AL6:AL13)</f>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="C9" s="22">
+        <f>SUM(Attendance!AL7:AL14)</f>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="11">
-        <f>SUM(Attendance!AM6:AM13)</f>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="C10" s="26">
+        <f>SUM(Attendance!AM7:AM14)</f>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="9">
-        <f>SUM(Attendance!AN6:AN13)</f>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="C11" s="22">
+        <f>SUM(Attendance!AN7:AN14)</f>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="31">
-        <f>SUM(B4:B10)</f>
-      </c>
-      <c r="C11" s="31" t="s">
+      <c r="C12" s="9">
+        <f>SUM(C5:C11)</f>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Italic"Explore Excel&amp;R&amp;"Calibri,Italic"Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/public/downloads/attendance-tracker.xlsx
+++ b/public/downloads/attendance-tracker.xlsx
@@ -49,7 +49,7 @@
     <t>The codes</t>
   </si>
   <si>
-    <t>P present, H holiday, S sick, L late, R remote, U unpaid leave, X public holiday. Each one colours its own cell so a month reads at a glance.</t>
+    <t>P present, V vacation, S sick, L late, R remote, U unpaid leave, X company holiday. Each one colours its own cell so a month reads at a glance.</t>
   </si>
   <si>
     <t>Why the dropdown matters</t>
@@ -58,7 +58,7 @@
     <t>A tracker breaks the moment someone types "p" one day and "Present" the next, because COUNTIF treats them as different values. The dropdown makes that impossible, which is why the whole grid carries one.</t>
   </si>
   <si>
-    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modelling convention.</t>
+    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modeling convention.</t>
   </si>
   <si>
     <t>Codes</t>
@@ -85,13 +85,13 @@
     <t>Working days</t>
   </si>
   <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>Holiday</t>
-  </si>
-  <si>
-    <t>Annual leave entitlement</t>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Vacation</t>
+  </si>
+  <si>
+    <t>Paid time off entitlement</t>
   </si>
   <si>
     <t>S</t>
@@ -130,7 +130,7 @@
     <t>X</t>
   </si>
   <si>
-    <t>Public holiday</t>
+    <t>Company holiday</t>
   </si>
   <si>
     <t>Not counted as absence</t>
@@ -958,7 +958,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -1084,7 +1084,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -1306,7 +1306,7 @@
         <f>COUNTIF($C7:$AG7,"P")</f>
       </c>
       <c r="AI7" s="25">
-        <f>COUNTIF($C7:$AG7,"H")</f>
+        <f>COUNTIF($C7:$AG7,"V")</f>
       </c>
       <c r="AJ7" s="25">
         <f>COUNTIF($C7:$AG7,"S")</f>
@@ -1366,7 +1366,7 @@
         <f>COUNTIF($C8:$AG8,"P")</f>
       </c>
       <c r="AI8" s="25">
-        <f>COUNTIF($C8:$AG8,"H")</f>
+        <f>COUNTIF($C8:$AG8,"V")</f>
       </c>
       <c r="AJ8" s="25">
         <f>COUNTIF($C8:$AG8,"S")</f>
@@ -1426,7 +1426,7 @@
         <f>COUNTIF($C9:$AG9,"P")</f>
       </c>
       <c r="AI9" s="25">
-        <f>COUNTIF($C9:$AG9,"H")</f>
+        <f>COUNTIF($C9:$AG9,"V")</f>
       </c>
       <c r="AJ9" s="25">
         <f>COUNTIF($C9:$AG9,"S")</f>
@@ -1486,7 +1486,7 @@
         <f>COUNTIF($C10:$AG10,"P")</f>
       </c>
       <c r="AI10" s="25">
-        <f>COUNTIF($C10:$AG10,"H")</f>
+        <f>COUNTIF($C10:$AG10,"V")</f>
       </c>
       <c r="AJ10" s="25">
         <f>COUNTIF($C10:$AG10,"S")</f>
@@ -1546,7 +1546,7 @@
         <f>COUNTIF($C11:$AG11,"P")</f>
       </c>
       <c r="AI11" s="25">
-        <f>COUNTIF($C11:$AG11,"H")</f>
+        <f>COUNTIF($C11:$AG11,"V")</f>
       </c>
       <c r="AJ11" s="25">
         <f>COUNTIF($C11:$AG11,"S")</f>
@@ -1606,7 +1606,7 @@
         <f>COUNTIF($C12:$AG12,"P")</f>
       </c>
       <c r="AI12" s="25">
-        <f>COUNTIF($C12:$AG12,"H")</f>
+        <f>COUNTIF($C12:$AG12,"V")</f>
       </c>
       <c r="AJ12" s="25">
         <f>COUNTIF($C12:$AG12,"S")</f>
@@ -1666,7 +1666,7 @@
         <f>COUNTIF($C13:$AG13,"P")</f>
       </c>
       <c r="AI13" s="25">
-        <f>COUNTIF($C13:$AG13,"H")</f>
+        <f>COUNTIF($C13:$AG13,"V")</f>
       </c>
       <c r="AJ13" s="25">
         <f>COUNTIF($C13:$AG13,"S")</f>
@@ -1726,7 +1726,7 @@
         <f>COUNTIF($C14:$AG14,"P")</f>
       </c>
       <c r="AI14" s="25">
-        <f>COUNTIF($C14:$AG14,"H")</f>
+        <f>COUNTIF($C14:$AG14,"V")</f>
       </c>
       <c r="AJ14" s="25">
         <f>COUNTIF($C14:$AG14,"S")</f>
@@ -1750,7 +1750,7 @@
       <formula>"P"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"H"</formula>
+      <formula>"V"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"S"</formula>
@@ -1773,12 +1773,12 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Unknown code" error="Use one of the codes listed on the Codes sheet." sqref="C7:AG14">
-      <formula1>"P,H,S,L,R,U,X"</formula1>
+      <formula1>"P,V,S,L,R,U,X"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -1945,7 +1945,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>

--- a/public/downloads/attendance-tracker.xlsx
+++ b/public/downloads/attendance-tracker.xlsx
@@ -14,174 +14,183 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="61">
+  <si>
+    <t>How this workbook works</t>
+  </si>
+  <si>
+    <t>Explore Excel  ·  exploreexcel.com</t>
+  </si>
+  <si>
+    <t>What this is</t>
+  </si>
   <si>
     <t>Attendance and leave tracker</t>
   </si>
   <si>
-    <t>How to use this template</t>
-  </si>
-  <si>
     <t>What this does</t>
   </si>
   <si>
     <t>Records daily attendance for a team across one month and totals every code automatically.</t>
   </si>
   <si>
+    <t>Using it</t>
+  </si>
+  <si>
+    <t>1. Set the month in the cream cell B3 on the Attendance sheet. Every column heading follows from it.</t>
+  </si>
+  <si>
+    <t>2. Replace the names in column B with your team.</t>
+  </si>
+  <si>
+    <t>3. Each day, pick a code from the dropdown. The totals on the right count themselves.</t>
+  </si>
+  <si>
+    <t>4. The Summary sheet totals the whole team.</t>
+  </si>
+  <si>
+    <t>The codes</t>
+  </si>
+  <si>
+    <t>P present, V vacation, S sick, L late, R remote, U unpaid leave, X company holiday. Each one colours its own cell so a month reads at a glance.</t>
+  </si>
+  <si>
+    <t>Why the dropdown matters</t>
+  </si>
+  <si>
+    <t>A tracker breaks the moment someone types "p" one day and "Present" the next, because COUNTIF treats them as different values. The dropdown makes that impossible, which is why the whole grid carries one.</t>
+  </si>
+  <si>
+    <t>Reading the colors</t>
+  </si>
+  <si>
+    <t>Blue figures are yours to type over. Black figures are calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modeling convention, so anyone in a finance or audit role will read it without being told.</t>
+  </si>
+  <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>Explore Excel  ·  exploreexcel.com  ·  The only values the grid accepts</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>Counts towards</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Present</t>
+  </si>
+  <si>
+    <t>Working days</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Vacation</t>
+  </si>
+  <si>
+    <t>Paid time off entitlement</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Sick</t>
+  </si>
+  <si>
+    <t>Sickness absence</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Late</t>
+  </si>
+  <si>
+    <t>Working days, flagged</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>Unpaid leave</t>
+  </si>
+  <si>
+    <t>Unpaid absence</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Company holiday</t>
+  </si>
+  <si>
+    <t>Not counted as absence</t>
+  </si>
+  <si>
+    <t>Attendance and leave</t>
+  </si>
+  <si>
+    <t>Explore Excel  ·  exploreexcel.com  ·  Set the month, then fill the grid from the dropdowns</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Adams, R</t>
+  </si>
+  <si>
+    <t>Brennan, T</t>
+  </si>
+  <si>
+    <t>Fischer, L</t>
+  </si>
+  <si>
+    <t>Okafor, J</t>
+  </si>
+  <si>
+    <t>Pritchard, O</t>
+  </si>
+  <si>
+    <t>Raman, P</t>
+  </si>
+  <si>
+    <t>Whitfield, S</t>
+  </si>
+  <si>
+    <t>Zhang, M</t>
+  </si>
+  <si>
+    <t>Month summary</t>
+  </si>
+  <si>
+    <t>Explore Excel  ·  exploreexcel.com  ·  Totals across the whole team</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>Using it</t>
-  </si>
-  <si>
-    <t>1. Set the month in the cream cell B3 on the Attendance sheet. Every column heading follows from it.</t>
-  </si>
-  <si>
-    <t>2. Replace the names in column B with your team.</t>
-  </si>
-  <si>
-    <t>3. Each day, pick a code from the dropdown. The totals on the right count themselves.</t>
-  </si>
-  <si>
-    <t>4. The Summary sheet totals the whole team.</t>
-  </si>
-  <si>
-    <t>The codes</t>
-  </si>
-  <si>
-    <t>P present, V vacation, S sick, L late, R remote, U unpaid leave, X company holiday. Each one colours its own cell so a month reads at a glance.</t>
-  </si>
-  <si>
-    <t>Why the dropdown matters</t>
-  </si>
-  <si>
-    <t>A tracker breaks the moment someone types "p" one day and "Present" the next, because COUNTIF treats them as different values. The dropdown makes that impossible, which is why the whole grid carries one.</t>
-  </si>
-  <si>
-    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modeling convention.</t>
-  </si>
-  <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>The only values the grid accepts</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Meaning</t>
-  </si>
-  <si>
-    <t>Counts towards</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>Working days</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Vacation</t>
-  </si>
-  <si>
-    <t>Paid time off entitlement</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>Sick</t>
-  </si>
-  <si>
-    <t>Sickness absence</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Late</t>
-  </si>
-  <si>
-    <t>Working days, flagged</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>Remote</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>Unpaid leave</t>
-  </si>
-  <si>
-    <t>Unpaid absence</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Company holiday</t>
-  </si>
-  <si>
-    <t>Not counted as absence</t>
-  </si>
-  <si>
-    <t>Attendance and leave</t>
-  </si>
-  <si>
-    <t>Set the month, then fill the grid from the dropdowns</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Adams, R</t>
-  </si>
-  <si>
-    <t>Brennan, T</t>
-  </si>
-  <si>
-    <t>Fischer, L</t>
-  </si>
-  <si>
-    <t>Okafor, J</t>
-  </si>
-  <si>
-    <t>Pritchard, O</t>
-  </si>
-  <si>
-    <t>Raman, P</t>
-  </si>
-  <si>
-    <t>Whitfield, S</t>
-  </si>
-  <si>
-    <t>Zhang, M</t>
-  </si>
-  <si>
-    <t>Month summary</t>
-  </si>
-  <si>
-    <t>Totals across the whole team</t>
-  </si>
-  <si>
-    <t>Days</t>
   </si>
   <si>
     <t>Total entries</t>
@@ -198,7 +207,7 @@
     <numFmt numFmtId="164" formatCode="mmmm yyyy"/>
     <numFmt numFmtId="165" formatCode="d"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -208,15 +217,14 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF0A4A3A"/>
-      <sz val="15"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
       <name val="Arial"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FF4A4A48"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
+      <color rgb="FFC6E4D9"/>
+      <sz val="9"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -227,13 +235,7 @@
     <font>
       <color rgb="FF141414"/>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF4A4A48"/>
-      <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -245,13 +247,13 @@
       <b/>
       <color rgb="FF4A4A48"/>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -262,19 +264,19 @@
     <font>
       <color rgb="FF0000FF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FF141414"/>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0A4A3A"/>
       <sz val="10"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="12">
@@ -283,11 +285,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F5EE"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -334,6 +331,11 @@
         <fgColor rgb="FFFFFDF0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F5EE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -362,77 +364,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -861,98 +852,100 @@
     <tabColor rgb="FF4A4A48"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:B20"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="94" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="B2" s="2"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+      <c r="C2" s="2"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+    <row r="5" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
+    <row r="7" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
+    <row r="8" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+    <row r="10" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
+    <row r="11" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+    <row r="13" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+    <row r="15" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
+    <row r="17" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+    <row r="19" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
+    <row r="20" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
+    <row r="22" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
+    <row r="23" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -979,106 +972,106 @@
     <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
+      <c r="B4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="A5" s="6" t="s">
         <v>22</v>
       </c>
+      <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>36</v>
       </c>
+      <c r="B10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="A11" s="14" t="s">
         <v>39</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1106,641 +1099,641 @@
     <col min="34" max="40" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="25.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
+        <v>42</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="19">
+      <c r="A3" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="16">
         <v>46023</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="21">
+      <c r="A6" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="18">
         <f>IF(MONTH($B$3+0)=MONTH($B$3),$B$3+0,"")</f>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="18">
         <f>IF(MONTH($B$3+1)=MONTH($B$3),$B$3+1,"")</f>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="18">
         <f>IF(MONTH($B$3+2)=MONTH($B$3),$B$3+2,"")</f>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="18">
         <f>IF(MONTH($B$3+3)=MONTH($B$3),$B$3+3,"")</f>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="18">
         <f>IF(MONTH($B$3+4)=MONTH($B$3),$B$3+4,"")</f>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="18">
         <f>IF(MONTH($B$3+5)=MONTH($B$3),$B$3+5,"")</f>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="18">
         <f>IF(MONTH($B$3+6)=MONTH($B$3),$B$3+6,"")</f>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="18">
         <f>IF(MONTH($B$3+7)=MONTH($B$3),$B$3+7,"")</f>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="18">
         <f>IF(MONTH($B$3+8)=MONTH($B$3),$B$3+8,"")</f>
       </c>
-      <c r="L6" s="21">
+      <c r="L6" s="18">
         <f>IF(MONTH($B$3+9)=MONTH($B$3),$B$3+9,"")</f>
       </c>
-      <c r="M6" s="21">
+      <c r="M6" s="18">
         <f>IF(MONTH($B$3+10)=MONTH($B$3),$B$3+10,"")</f>
       </c>
-      <c r="N6" s="21">
+      <c r="N6" s="18">
         <f>IF(MONTH($B$3+11)=MONTH($B$3),$B$3+11,"")</f>
       </c>
-      <c r="O6" s="21">
+      <c r="O6" s="18">
         <f>IF(MONTH($B$3+12)=MONTH($B$3),$B$3+12,"")</f>
       </c>
-      <c r="P6" s="21">
+      <c r="P6" s="18">
         <f>IF(MONTH($B$3+13)=MONTH($B$3),$B$3+13,"")</f>
       </c>
-      <c r="Q6" s="21">
+      <c r="Q6" s="18">
         <f>IF(MONTH($B$3+14)=MONTH($B$3),$B$3+14,"")</f>
       </c>
-      <c r="R6" s="21">
+      <c r="R6" s="18">
         <f>IF(MONTH($B$3+15)=MONTH($B$3),$B$3+15,"")</f>
       </c>
-      <c r="S6" s="21">
+      <c r="S6" s="18">
         <f>IF(MONTH($B$3+16)=MONTH($B$3),$B$3+16,"")</f>
       </c>
-      <c r="T6" s="21">
+      <c r="T6" s="18">
         <f>IF(MONTH($B$3+17)=MONTH($B$3),$B$3+17,"")</f>
       </c>
-      <c r="U6" s="21">
+      <c r="U6" s="18">
         <f>IF(MONTH($B$3+18)=MONTH($B$3),$B$3+18,"")</f>
       </c>
-      <c r="V6" s="21">
+      <c r="V6" s="18">
         <f>IF(MONTH($B$3+19)=MONTH($B$3),$B$3+19,"")</f>
       </c>
-      <c r="W6" s="21">
+      <c r="W6" s="18">
         <f>IF(MONTH($B$3+20)=MONTH($B$3),$B$3+20,"")</f>
       </c>
-      <c r="X6" s="21">
+      <c r="X6" s="18">
         <f>IF(MONTH($B$3+21)=MONTH($B$3),$B$3+21,"")</f>
       </c>
-      <c r="Y6" s="21">
+      <c r="Y6" s="18">
         <f>IF(MONTH($B$3+22)=MONTH($B$3),$B$3+22,"")</f>
       </c>
-      <c r="Z6" s="21">
+      <c r="Z6" s="18">
         <f>IF(MONTH($B$3+23)=MONTH($B$3),$B$3+23,"")</f>
       </c>
-      <c r="AA6" s="21">
+      <c r="AA6" s="18">
         <f>IF(MONTH($B$3+24)=MONTH($B$3),$B$3+24,"")</f>
       </c>
-      <c r="AB6" s="21">
+      <c r="AB6" s="18">
         <f>IF(MONTH($B$3+25)=MONTH($B$3),$B$3+25,"")</f>
       </c>
-      <c r="AC6" s="21">
+      <c r="AC6" s="18">
         <f>IF(MONTH($B$3+26)=MONTH($B$3),$B$3+26,"")</f>
       </c>
-      <c r="AD6" s="21">
+      <c r="AD6" s="18">
         <f>IF(MONTH($B$3+27)=MONTH($B$3),$B$3+27,"")</f>
       </c>
-      <c r="AE6" s="21">
+      <c r="AE6" s="18">
         <f>IF(MONTH($B$3+28)=MONTH($B$3),$B$3+28,"")</f>
       </c>
-      <c r="AF6" s="21">
+      <c r="AF6" s="18">
         <f>IF(MONTH($B$3+29)=MONTH($B$3),$B$3+29,"")</f>
       </c>
-      <c r="AG6" s="21">
+      <c r="AG6" s="18">
         <f>IF(MONTH($B$3+30)=MONTH($B$3),$B$3+30,"")</f>
       </c>
-      <c r="AH6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="AK6" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="AL6" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="AM6" s="16" t="s">
+      <c r="AH6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AL6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AN6" s="17" t="s">
-        <v>37</v>
+      <c r="AM6" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN6" s="14" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="19">
         <v>1</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24"/>
-      <c r="X7" s="24"/>
-      <c r="Y7" s="24"/>
-      <c r="Z7" s="24"/>
-      <c r="AA7" s="24"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="24"/>
-      <c r="AD7" s="24"/>
-      <c r="AE7" s="24"/>
-      <c r="AF7" s="24"/>
-      <c r="AG7" s="24"/>
-      <c r="AH7" s="25">
+      <c r="B7" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="21"/>
+      <c r="W7" s="21"/>
+      <c r="X7" s="21"/>
+      <c r="Y7" s="21"/>
+      <c r="Z7" s="21"/>
+      <c r="AA7" s="21"/>
+      <c r="AB7" s="21"/>
+      <c r="AC7" s="21"/>
+      <c r="AD7" s="21"/>
+      <c r="AE7" s="21"/>
+      <c r="AF7" s="21"/>
+      <c r="AG7" s="21"/>
+      <c r="AH7" s="22">
         <f>COUNTIF($C7:$AG7,"P")</f>
       </c>
-      <c r="AI7" s="25">
+      <c r="AI7" s="22">
         <f>COUNTIF($C7:$AG7,"V")</f>
       </c>
-      <c r="AJ7" s="25">
+      <c r="AJ7" s="22">
         <f>COUNTIF($C7:$AG7,"S")</f>
       </c>
-      <c r="AK7" s="25">
+      <c r="AK7" s="22">
         <f>COUNTIF($C7:$AG7,"L")</f>
       </c>
-      <c r="AL7" s="25">
+      <c r="AL7" s="22">
         <f>COUNTIF($C7:$AG7,"R")</f>
       </c>
-      <c r="AM7" s="25">
+      <c r="AM7" s="22">
         <f>COUNTIF($C7:$AG7,"U")</f>
       </c>
-      <c r="AN7" s="25">
+      <c r="AN7" s="22">
         <f>COUNTIF($C7:$AG7,"X")</f>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A8" s="22">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
-      <c r="B8" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="24"/>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="24"/>
-      <c r="AG8" s="24"/>
-      <c r="AH8" s="25">
+      <c r="B8" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="21"/>
+      <c r="W8" s="21"/>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="21"/>
+      <c r="AA8" s="21"/>
+      <c r="AB8" s="21"/>
+      <c r="AC8" s="21"/>
+      <c r="AD8" s="21"/>
+      <c r="AE8" s="21"/>
+      <c r="AF8" s="21"/>
+      <c r="AG8" s="21"/>
+      <c r="AH8" s="22">
         <f>COUNTIF($C8:$AG8,"P")</f>
       </c>
-      <c r="AI8" s="25">
+      <c r="AI8" s="22">
         <f>COUNTIF($C8:$AG8,"V")</f>
       </c>
-      <c r="AJ8" s="25">
+      <c r="AJ8" s="22">
         <f>COUNTIF($C8:$AG8,"S")</f>
       </c>
-      <c r="AK8" s="25">
+      <c r="AK8" s="22">
         <f>COUNTIF($C8:$AG8,"L")</f>
       </c>
-      <c r="AL8" s="25">
+      <c r="AL8" s="22">
         <f>COUNTIF($C8:$AG8,"R")</f>
       </c>
-      <c r="AM8" s="25">
+      <c r="AM8" s="22">
         <f>COUNTIF($C8:$AG8,"U")</f>
       </c>
-      <c r="AN8" s="25">
+      <c r="AN8" s="22">
         <f>COUNTIF($C8:$AG8,"X")</f>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
+      <c r="A9" s="19">
         <v>3</v>
       </c>
-      <c r="B9" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="24"/>
-      <c r="X9" s="24"/>
-      <c r="Y9" s="24"/>
-      <c r="Z9" s="24"/>
-      <c r="AA9" s="24"/>
-      <c r="AB9" s="24"/>
-      <c r="AC9" s="24"/>
-      <c r="AD9" s="24"/>
-      <c r="AE9" s="24"/>
-      <c r="AF9" s="24"/>
-      <c r="AG9" s="24"/>
-      <c r="AH9" s="25">
+      <c r="B9" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="21"/>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="21"/>
+      <c r="AA9" s="21"/>
+      <c r="AB9" s="21"/>
+      <c r="AC9" s="21"/>
+      <c r="AD9" s="21"/>
+      <c r="AE9" s="21"/>
+      <c r="AF9" s="21"/>
+      <c r="AG9" s="21"/>
+      <c r="AH9" s="22">
         <f>COUNTIF($C9:$AG9,"P")</f>
       </c>
-      <c r="AI9" s="25">
+      <c r="AI9" s="22">
         <f>COUNTIF($C9:$AG9,"V")</f>
       </c>
-      <c r="AJ9" s="25">
+      <c r="AJ9" s="22">
         <f>COUNTIF($C9:$AG9,"S")</f>
       </c>
-      <c r="AK9" s="25">
+      <c r="AK9" s="22">
         <f>COUNTIF($C9:$AG9,"L")</f>
       </c>
-      <c r="AL9" s="25">
+      <c r="AL9" s="22">
         <f>COUNTIF($C9:$AG9,"R")</f>
       </c>
-      <c r="AM9" s="25">
+      <c r="AM9" s="22">
         <f>COUNTIF($C9:$AG9,"U")</f>
       </c>
-      <c r="AN9" s="25">
+      <c r="AN9" s="22">
         <f>COUNTIF($C9:$AG9,"X")</f>
       </c>
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+      <c r="A10" s="19">
         <v>4</v>
       </c>
-      <c r="B10" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="24"/>
-      <c r="X10" s="24"/>
-      <c r="Y10" s="24"/>
-      <c r="Z10" s="24"/>
-      <c r="AA10" s="24"/>
-      <c r="AB10" s="24"/>
-      <c r="AC10" s="24"/>
-      <c r="AD10" s="24"/>
-      <c r="AE10" s="24"/>
-      <c r="AF10" s="24"/>
-      <c r="AG10" s="24"/>
-      <c r="AH10" s="25">
+      <c r="B10" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="21"/>
+      <c r="W10" s="21"/>
+      <c r="X10" s="21"/>
+      <c r="Y10" s="21"/>
+      <c r="Z10" s="21"/>
+      <c r="AA10" s="21"/>
+      <c r="AB10" s="21"/>
+      <c r="AC10" s="21"/>
+      <c r="AD10" s="21"/>
+      <c r="AE10" s="21"/>
+      <c r="AF10" s="21"/>
+      <c r="AG10" s="21"/>
+      <c r="AH10" s="22">
         <f>COUNTIF($C10:$AG10,"P")</f>
       </c>
-      <c r="AI10" s="25">
+      <c r="AI10" s="22">
         <f>COUNTIF($C10:$AG10,"V")</f>
       </c>
-      <c r="AJ10" s="25">
+      <c r="AJ10" s="22">
         <f>COUNTIF($C10:$AG10,"S")</f>
       </c>
-      <c r="AK10" s="25">
+      <c r="AK10" s="22">
         <f>COUNTIF($C10:$AG10,"L")</f>
       </c>
-      <c r="AL10" s="25">
+      <c r="AL10" s="22">
         <f>COUNTIF($C10:$AG10,"R")</f>
       </c>
-      <c r="AM10" s="25">
+      <c r="AM10" s="22">
         <f>COUNTIF($C10:$AG10,"U")</f>
       </c>
-      <c r="AN10" s="25">
+      <c r="AN10" s="22">
         <f>COUNTIF($C10:$AG10,"X")</f>
       </c>
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A11" s="22">
+      <c r="A11" s="19">
         <v>5</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="24"/>
-      <c r="V11" s="24"/>
-      <c r="W11" s="24"/>
-      <c r="X11" s="24"/>
-      <c r="Y11" s="24"/>
-      <c r="Z11" s="24"/>
-      <c r="AA11" s="24"/>
-      <c r="AB11" s="24"/>
-      <c r="AC11" s="24"/>
-      <c r="AD11" s="24"/>
-      <c r="AE11" s="24"/>
-      <c r="AF11" s="24"/>
-      <c r="AG11" s="24"/>
-      <c r="AH11" s="25">
+      <c r="B11" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="21"/>
+      <c r="W11" s="21"/>
+      <c r="X11" s="21"/>
+      <c r="Y11" s="21"/>
+      <c r="Z11" s="21"/>
+      <c r="AA11" s="21"/>
+      <c r="AB11" s="21"/>
+      <c r="AC11" s="21"/>
+      <c r="AD11" s="21"/>
+      <c r="AE11" s="21"/>
+      <c r="AF11" s="21"/>
+      <c r="AG11" s="21"/>
+      <c r="AH11" s="22">
         <f>COUNTIF($C11:$AG11,"P")</f>
       </c>
-      <c r="AI11" s="25">
+      <c r="AI11" s="22">
         <f>COUNTIF($C11:$AG11,"V")</f>
       </c>
-      <c r="AJ11" s="25">
+      <c r="AJ11" s="22">
         <f>COUNTIF($C11:$AG11,"S")</f>
       </c>
-      <c r="AK11" s="25">
+      <c r="AK11" s="22">
         <f>COUNTIF($C11:$AG11,"L")</f>
       </c>
-      <c r="AL11" s="25">
+      <c r="AL11" s="22">
         <f>COUNTIF($C11:$AG11,"R")</f>
       </c>
-      <c r="AM11" s="25">
+      <c r="AM11" s="22">
         <f>COUNTIF($C11:$AG11,"U")</f>
       </c>
-      <c r="AN11" s="25">
+      <c r="AN11" s="22">
         <f>COUNTIF($C11:$AG11,"X")</f>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A12" s="22">
+      <c r="A12" s="19">
         <v>6</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="24"/>
-      <c r="Y12" s="24"/>
-      <c r="Z12" s="24"/>
-      <c r="AA12" s="24"/>
-      <c r="AB12" s="24"/>
-      <c r="AC12" s="24"/>
-      <c r="AD12" s="24"/>
-      <c r="AE12" s="24"/>
-      <c r="AF12" s="24"/>
-      <c r="AG12" s="24"/>
-      <c r="AH12" s="25">
+      <c r="B12" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="21"/>
+      <c r="AA12" s="21"/>
+      <c r="AB12" s="21"/>
+      <c r="AC12" s="21"/>
+      <c r="AD12" s="21"/>
+      <c r="AE12" s="21"/>
+      <c r="AF12" s="21"/>
+      <c r="AG12" s="21"/>
+      <c r="AH12" s="22">
         <f>COUNTIF($C12:$AG12,"P")</f>
       </c>
-      <c r="AI12" s="25">
+      <c r="AI12" s="22">
         <f>COUNTIF($C12:$AG12,"V")</f>
       </c>
-      <c r="AJ12" s="25">
+      <c r="AJ12" s="22">
         <f>COUNTIF($C12:$AG12,"S")</f>
       </c>
-      <c r="AK12" s="25">
+      <c r="AK12" s="22">
         <f>COUNTIF($C12:$AG12,"L")</f>
       </c>
-      <c r="AL12" s="25">
+      <c r="AL12" s="22">
         <f>COUNTIF($C12:$AG12,"R")</f>
       </c>
-      <c r="AM12" s="25">
+      <c r="AM12" s="22">
         <f>COUNTIF($C12:$AG12,"U")</f>
       </c>
-      <c r="AN12" s="25">
+      <c r="AN12" s="22">
         <f>COUNTIF($C12:$AG12,"X")</f>
       </c>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A13" s="22">
+      <c r="A13" s="19">
         <v>7</v>
       </c>
-      <c r="B13" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
-      <c r="V13" s="24"/>
-      <c r="W13" s="24"/>
-      <c r="X13" s="24"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="24"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="24"/>
-      <c r="AC13" s="24"/>
-      <c r="AD13" s="24"/>
-      <c r="AE13" s="24"/>
-      <c r="AF13" s="24"/>
-      <c r="AG13" s="24"/>
-      <c r="AH13" s="25">
+      <c r="B13" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="21"/>
+      <c r="AA13" s="21"/>
+      <c r="AB13" s="21"/>
+      <c r="AC13" s="21"/>
+      <c r="AD13" s="21"/>
+      <c r="AE13" s="21"/>
+      <c r="AF13" s="21"/>
+      <c r="AG13" s="21"/>
+      <c r="AH13" s="22">
         <f>COUNTIF($C13:$AG13,"P")</f>
       </c>
-      <c r="AI13" s="25">
+      <c r="AI13" s="22">
         <f>COUNTIF($C13:$AG13,"V")</f>
       </c>
-      <c r="AJ13" s="25">
+      <c r="AJ13" s="22">
         <f>COUNTIF($C13:$AG13,"S")</f>
       </c>
-      <c r="AK13" s="25">
+      <c r="AK13" s="22">
         <f>COUNTIF($C13:$AG13,"L")</f>
       </c>
-      <c r="AL13" s="25">
+      <c r="AL13" s="22">
         <f>COUNTIF($C13:$AG13,"R")</f>
       </c>
-      <c r="AM13" s="25">
+      <c r="AM13" s="22">
         <f>COUNTIF($C13:$AG13,"U")</f>
       </c>
-      <c r="AN13" s="25">
+      <c r="AN13" s="22">
         <f>COUNTIF($C13:$AG13,"X")</f>
       </c>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="A14" s="19">
         <v>8</v>
       </c>
-      <c r="B14" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="24"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="24"/>
-      <c r="AH14" s="25">
+      <c r="B14" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21"/>
+      <c r="AH14" s="22">
         <f>COUNTIF($C14:$AG14,"P")</f>
       </c>
-      <c r="AI14" s="25">
+      <c r="AI14" s="22">
         <f>COUNTIF($C14:$AG14,"V")</f>
       </c>
-      <c r="AJ14" s="25">
+      <c r="AJ14" s="22">
         <f>COUNTIF($C14:$AG14,"S")</f>
       </c>
-      <c r="AK14" s="25">
+      <c r="AK14" s="22">
         <f>COUNTIF($C14:$AG14,"L")</f>
       </c>
-      <c r="AL14" s="25">
+      <c r="AL14" s="22">
         <f>COUNTIF($C14:$AG14,"R")</f>
       </c>
-      <c r="AM14" s="25">
+      <c r="AM14" s="22">
         <f>COUNTIF($C14:$AG14,"U")</f>
       </c>
-      <c r="AN14" s="25">
+      <c r="AN14" s="22">
         <f>COUNTIF($C14:$AG14,"X")</f>
       </c>
     </row>
@@ -1800,146 +1793,146 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="25.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
+      <c r="B4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="22">
+      <c r="A5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="19">
         <f>SUM(Attendance!AH7:AH14)</f>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>22</v>
+      <c r="D5" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="23">
+        <f>SUM(Attendance!AI7:AI14)</f>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="19">
+        <f>SUM(Attendance!AJ7:AJ14)</f>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="23">
+        <f>SUM(Attendance!AK7:AK14)</f>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="19">
+        <f>SUM(Attendance!AL7:AL14)</f>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="26">
-        <f>SUM(Attendance!AI7:AI14)</f>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="22">
-        <f>SUM(Attendance!AJ7:AJ14)</f>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="26">
-        <f>SUM(Attendance!AK7:AK14)</f>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="22">
-        <f>SUM(Attendance!AL7:AL14)</f>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="26">
+      <c r="A10" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="23">
         <f>SUM(Attendance!AM7:AM14)</f>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>36</v>
+      <c r="D10" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="22">
+      <c r="A11" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="19">
         <f>SUM(Attendance!AN7:AN14)</f>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>39</v>
+      <c r="D11" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="9">
+      <c r="A12" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="6">
         <f>SUM(C5:C11)</f>
       </c>
-      <c r="D12" s="27" t="s">
-        <v>57</v>
+      <c r="D12" s="24" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/attendance-tracker.xlsx
+++ b/public/downloads/attendance-tracker.xlsx
@@ -852,33 +852,28 @@
     <tabColor rgb="FF4A4A48"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="3" width="30" customWidth="1"/>
+    <col min="1" max="1" width="104" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="25.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -888,7 +883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
@@ -898,22 +893,22 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
@@ -923,7 +918,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>12</v>
       </c>
@@ -933,7 +928,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" ht="42.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>14</v>
       </c>
@@ -943,7 +938,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" ht="42.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>16</v>
       </c>
